--- a/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
@@ -577,7 +577,7 @@
         <v>0.456</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F2" t="n">
         <v>0.122</v>
@@ -599,7 +599,7 @@
         <v>-0.257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>-0.151</v>
@@ -621,7 +621,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008</v>
+        <v>0.022</v>
       </c>
       <c r="F4" t="n">
         <v>0.181</v>
@@ -634,19 +634,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008</v>
+        <v>0.022</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.274</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +665,7 @@
         <v>0.181</v>
       </c>
       <c r="E6" t="n">
-        <v>0.274</v>
+        <v>0.247</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>

--- a/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
@@ -577,7 +577,7 @@
         <v>0.456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F2" t="n">
         <v>0.122</v>
@@ -599,7 +599,7 @@
         <v>-0.257</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
         <v>-0.151</v>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
         <v>0.022</v>
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.247</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +665,7 @@
         <v>0.181</v>
       </c>
       <c r="E6" t="n">
-        <v>0.247</v>
+        <v>0.249</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>

--- a/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="component_availability" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="component_correlations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="stable_core_counts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="K_degree_sensitivity" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -599,7 +601,7 @@
         <v>-0.257</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="F3" t="n">
         <v>-0.151</v>
@@ -637,7 +639,7 @@
         <v>0.001</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="D5" t="n">
         <v>0.022</v>
@@ -669,6 +671,304 @@
       </c>
       <c r="F6" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>progression_class</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>genes_in_class</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>weight_samples</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>genes_meeting_threshold</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>max_frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1822</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fibrosis-only</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>inflammation-only</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2377</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>degree_quintile</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>genes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mean_K</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>percent_with_any_K</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_nondrug_degree</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>spearman_K_vs_degree</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>spearman_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q1 least connected</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.016</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.13e-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.511</v>
+      </c>
+      <c r="E3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2.13e-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.093</v>
+      </c>
+      <c r="E4" t="n">
+        <v>114</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2.13e-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.148</v>
+      </c>
+      <c r="E5" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.13e-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Q5 most connected</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="D6" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="E6" t="n">
+        <v>330</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.13e-86</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task6_target_scoring/task6_supporting.xlsx
@@ -601,7 +601,7 @@
         <v>-0.257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
         <v>-0.151</v>
@@ -639,7 +639,7 @@
         <v>0.001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
         <v>0.022</v>
@@ -779,7 +779,7 @@
         <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -859,7 +859,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.13e-86</t>
+          <t>1.60e-86</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v>1244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="D3" t="n">
         <v>6.511</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.13e-86</t>
+          <t>1.60e-86</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         <v>1244</v>
       </c>
       <c r="C4" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="D4" t="n">
         <v>11.093</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.13e-86</t>
+          <t>1.60e-86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         <v>1244</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="D5" t="n">
         <v>14.148</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.13e-86</t>
+          <t>1.60e-86</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1245</v>
       </c>
       <c r="C6" t="n">
-        <v>0.174</v>
+        <v>0.178</v>
       </c>
       <c r="D6" t="n">
         <v>27.39</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.13e-86</t>
+          <t>1.60e-86</t>
         </is>
       </c>
     </row>
